--- a/data/derived_data/5_SBMclustering/Dataset_2/ps_16S_rare_D2_tax_table.xlsx
+++ b/data/derived_data/5_SBMclustering/Dataset_2/ps_16S_rare_D2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">Burkholderiales</t>
   </si>
   <si>
-    <t xml:space="preserve">Burkholderiaceae_105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robbsia_105</t>
+    <t xml:space="preserve">Burkholderiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robbsia</t>
   </si>
   <si>
     <t xml:space="preserve">Unknown</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">Acetobacterales</t>
   </si>
   <si>
-    <t xml:space="preserve">Acetobacteraceae_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gluconobacter_11</t>
+    <t xml:space="preserve">Acetobacteraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gluconobacter</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
-    <t xml:space="preserve">Oxalobacteraceae_113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massilia_113</t>
+    <t xml:space="preserve">Oxalobacteraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massilia</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_1389</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">Bacillales</t>
   </si>
   <si>
-    <t xml:space="preserve">Planococcaceae_1389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_1389_1389</t>
+    <t xml:space="preserve">Planococcaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_1389</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_14</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">Lactobacillales</t>
   </si>
   <si>
-    <t xml:space="preserve">Lactobacillaceae_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levilactobacillus_14</t>
+    <t xml:space="preserve">Lactobacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levilactobacillus</t>
   </si>
   <si>
     <t xml:space="preserve">Lactobacillus brevis</t>
@@ -122,10 +122,7 @@
     <t xml:space="preserve">Cluster_1533</t>
   </si>
   <si>
-    <t xml:space="preserve">Planococcaceae_1533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lysinibacillus_1533</t>
+    <t xml:space="preserve">Lysinibacillus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_16</t>
@@ -134,19 +131,16 @@
     <t xml:space="preserve">Enterobacterales</t>
   </si>
   <si>
-    <t xml:space="preserve">Erwiniaceae_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_16_16</t>
+    <t xml:space="preserve">Erwiniaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_16</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
-    <t xml:space="preserve">Acetobacteraceae_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetobacter_20</t>
+    <t xml:space="preserve">Acetobacter</t>
   </si>
   <si>
     <t xml:space="preserve">Acetobacter thailandicus</t>
@@ -155,7 +149,7 @@
     <t xml:space="preserve">Cluster_21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_21_21</t>
+    <t xml:space="preserve">Unknown_21</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_2281</t>
@@ -164,40 +158,34 @@
     <t xml:space="preserve">Paenibacillales</t>
   </si>
   <si>
-    <t xml:space="preserve">Paenibacillaceae_2281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paenibacillus_2281</t>
+    <t xml:space="preserve">Paenibacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paenibacillus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_23</t>
   </si>
   <si>
-    <t xml:space="preserve">Planococcaceae_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lysinibacillus_23</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_26</t>
   </si>
   <si>
     <t xml:space="preserve">Pseudomonadales</t>
   </si>
   <si>
-    <t xml:space="preserve">Moraxellaceae_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_26_26</t>
+    <t xml:space="preserve">Moraxellaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_26</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_2821</t>
   </si>
   <si>
-    <t xml:space="preserve">Bacillaceae_2821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bacillus_2821</t>
+    <t xml:space="preserve">Bacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillus</t>
   </si>
   <si>
     <t xml:space="preserve">Bacillus acidicola</t>
@@ -206,10 +194,7 @@
     <t xml:space="preserve">Cluster_31</t>
   </si>
   <si>
-    <t xml:space="preserve">Acetobacteraceae_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neokomagataea_31</t>
+    <t xml:space="preserve">Neokomagataea</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_320</t>
@@ -224,142 +209,85 @@
     <t xml:space="preserve">Kitasatosporales</t>
   </si>
   <si>
-    <t xml:space="preserve">Streptomycetaceae_320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streptomyces_320</t>
+    <t xml:space="preserve">Streptomycetaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptomyces</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_337</t>
   </si>
   <si>
-    <t xml:space="preserve">Erwiniaceae_337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tatumella_337</t>
+    <t xml:space="preserve">Tatumella</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
-    <t xml:space="preserve">Pseudomonadaceae_35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pseudomonas_35</t>
+    <t xml:space="preserve">Pseudomonadaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pseudomonas</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_39</t>
   </si>
   <si>
-    <t xml:space="preserve">Moraxellaceae_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acinetobacter_39</t>
+    <t xml:space="preserve">Acinetobacter</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_449</t>
   </si>
   <si>
-    <t xml:space="preserve">Paenibacillaceae_449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paenibacillus_449</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_47</t>
   </si>
   <si>
-    <t xml:space="preserve">Oxalobacteraceae_47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massilia_47</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Erwiniaceae_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tatumella_5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_516</t>
   </si>
   <si>
-    <t xml:space="preserve">Orbaceae_516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_516_516</t>
+    <t xml:space="preserve">Orbaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_516</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_53</t>
   </si>
   <si>
-    <t xml:space="preserve">Bacillaceae_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bacillus_53</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
-    <t xml:space="preserve">Oxalobacteraceae_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massilia_55</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Acetobacteraceae_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gluconobacter_6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gluconobacter cerinus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Acetobacteraceae_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetobacter_7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_79</t>
   </si>
   <si>
     <t xml:space="preserve">Sphingomonadales</t>
   </si>
   <si>
-    <t xml:space="preserve">Sphingomonadaceae_79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sphingomonas_79</t>
+    <t xml:space="preserve">Sphingomonadaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_9</t>
   </si>
   <si>
-    <t xml:space="preserve">Acetobacteraceae_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetobacter_9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_93</t>
   </si>
   <si>
-    <t xml:space="preserve">Bacillaceae_93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shouchella_93</t>
+    <t xml:space="preserve">Shouchella</t>
   </si>
 </sst>
 </file>
@@ -861,10 +789,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -872,7 +800,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -884,13 +812,13 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -898,7 +826,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -913,18 +841,18 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
         <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -936,13 +864,13 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -950,7 +878,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -962,13 +890,13 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
         <v>49</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>51</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -976,7 +904,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -991,10 +919,10 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -1002,7 +930,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -1014,13 +942,13 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -1028,7 +956,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1043,18 +971,18 @@
         <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1069,10 +997,10 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -1080,25 +1008,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" t="s">
         <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" t="s">
-        <v>71</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -1106,7 +1034,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1118,13 +1046,13 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
         <v>39</v>
       </c>
-      <c r="F17" t="s">
-        <v>73</v>
-      </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -1132,7 +1060,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1144,13 +1072,13 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -1158,7 +1086,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -1170,13 +1098,13 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -1184,7 +1112,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1196,13 +1124,13 @@
         <v>26</v>
       </c>
       <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" t="s">
         <v>49</v>
-      </c>
-      <c r="F20" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" t="s">
-        <v>83</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -1210,7 +1138,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1225,10 +1153,10 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -1236,7 +1164,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
@@ -1248,13 +1176,13 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s">
         <v>39</v>
       </c>
-      <c r="F22" t="s">
-        <v>88</v>
-      </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -1262,7 +1190,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -1274,13 +1202,13 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -1288,7 +1216,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -1303,10 +1231,10 @@
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -1314,7 +1242,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -1329,10 +1257,10 @@
         <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -1340,7 +1268,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -1355,18 +1283,18 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -1381,10 +1309,10 @@
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -1392,7 +1320,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
@@ -1404,13 +1332,13 @@
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -1418,7 +1346,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -1433,18 +1361,18 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="H29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -1459,10 +1387,10 @@
         <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="G30" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
